--- a/outputs/apexbrasil_relatorio_qualidade.xlsx
+++ b/outputs/apexbrasil_relatorio_qualidade.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-16 14:34:47</t>
+          <t>2026-09-29 16:21:00</t>
         </is>
       </c>
     </row>
